--- a/basedatos_partidas/salida/descompuestos/07.04.01.070.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.01.070.xlsx
@@ -584,10 +584,10 @@
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>67.72</v>
+        <v>68.03</v>
       </c>
       <c r="H25" t="n">
         <v>0.68</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
   </sheetData>
